--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487860_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487860_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8764</v>
+        <v>3.9424</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2406</v>
+        <v>2.4271</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6358</v>
+        <v>1.5153</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4391</v>
+        <v>2.7481</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1444</v>
+        <v>2.9718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2947</v>
+        <v>-0.2237</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6106</v>
+        <v>3.3157</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9609</v>
+        <v>4.0783</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3504</v>
+        <v>-0.7625</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8286</v>
+        <v>-0.5676</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8165</v>
+        <v>-1.1064</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6451</v>
+        <v>0.5389</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8535</v>
+        <v>1.008</v>
       </c>
       <c r="T2" t="n">
-        <v>1.295</v>
+        <v>0.3601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5585</v>
+        <v>0.6479</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6247</v>
+        <v>3.8033</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9332</v>
+        <v>1.4905</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6914</v>
+        <v>2.3129</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7481</v>
+        <v>2.4391</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9718</v>
+        <v>2.1444</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2237</v>
+        <v>0.2947</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3157</v>
+        <v>1.6106</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0783</v>
+        <v>2.9609</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7625</v>
+        <v>-1.3504</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5676</v>
+        <v>0.8286</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1064</v>
+        <v>-0.8165</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5389</v>
+        <v>1.6451</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6903</v>
+        <v>0.7804</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1338</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.824</v>
+        <v>0.2356</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.354</v>
+        <v>3.2566</v>
       </c>
       <c r="E4" t="n">
-        <v>0.821</v>
+        <v>2.1992</v>
       </c>
       <c r="F4" t="n">
-        <v>2.533</v>
+        <v>1.0574</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7624</v>
+        <v>2.4232</v>
       </c>
       <c r="H4" t="n">
-        <v>0.181</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5814</v>
+        <v>1.2932</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4115</v>
+        <v>3.2276</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0465</v>
+        <v>2.1875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3649</v>
+        <v>1.0401</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3509</v>
+        <v>-0.8043</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8655</v>
+        <v>-1.0574</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2165</v>
+        <v>0.2531</v>
       </c>
       <c r="P4" t="n">
         <v>-1.2487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-2.2893</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1327</v>
+        <v>0.3308</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4907</v>
+        <v>0.2172</v>
       </c>
       <c r="U4" t="n">
-        <v>0.642</v>
+        <v>0.1136</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7076</v>
+        <v>1.7513</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="X4" t="n">
         <v>0.7076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2597</v>
+        <v>3.2445</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0373</v>
+        <v>1.002</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7776</v>
+        <v>2.2425</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2653</v>
+        <v>1.6276</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8186</v>
+        <v>0.4242</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4467</v>
+        <v>1.2034</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4166</v>
+        <v>0.6929</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2598</v>
+        <v>0.955</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1568</v>
+        <v>-0.2621</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1512</v>
+        <v>0.9347</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4412</v>
+        <v>-0.5308</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.4655</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4939</v>
+        <v>0.3681</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4501</v>
+        <v>0.0791</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0438</v>
+        <v>0.2891</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2112</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3351</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5755</v>
+        <v>2.8311</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3419</v>
+        <v>3.6087</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2336</v>
+        <v>-0.7776</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4232</v>
+        <v>2.2653</v>
       </c>
       <c r="H6" t="n">
-        <v>1.13</v>
+        <v>0.8186</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2932</v>
+        <v>1.4467</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2276</v>
+        <v>2.4166</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1875</v>
+        <v>2.2598</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0401</v>
+        <v>0.1568</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8043</v>
+        <v>-0.1512</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0574</v>
+        <v>-1.4412</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2531</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3503</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.64</v>
+        <v>0.0215</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2897</v>
+        <v>0.0438</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7513</v>
+        <v>-0.1238</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0437</v>
+        <v>2.2112</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7076</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3564</v>
+        <v>2.0476</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4662</v>
+        <v>-0.2506</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8902</v>
+        <v>2.2982</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6276</v>
+        <v>1.7624</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4242</v>
+        <v>0.181</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2034</v>
+        <v>1.5814</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929</v>
+        <v>1.4115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.955</v>
+        <v>1.0465</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2621</v>
+        <v>0.3649</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9347</v>
+        <v>0.3509</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5308</v>
+        <v>-0.8655</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4655</v>
+        <v>1.2165</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2487</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.52</v>
+        <v>0.8263</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4567</v>
+        <v>0.4191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0633</v>
+        <v>0.4071</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7726</v>
+        <v>1.686</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1724</v>
+        <v>1.8509</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3998</v>
+        <v>-0.1649</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1609</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0386</v>
+        <v>0.952</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7111</v>
+        <v>0.3896</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3275</v>
+        <v>0.5624</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3538</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5055</v>
+        <v>0.7326</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4297</v>
+        <v>0.7449</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4924</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5411</v>
+        <v>1.7682</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6988</v>
+        <v>1.014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8423</v>
+        <v>0.7542</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6297</v>
+        <v>0.3085</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.009</v>
+        <v>-0.9922</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3793</v>
+        <v>1.3007</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2559</v>
+        <v>-1.9341</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0298</v>
+        <v>-1.7358</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2857</v>
+        <v>-0.1984</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0192</v>
+        <v>-1.2808</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0192</v>
+        <v>-0.7232</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.5576</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2367</v>
+        <v>-0.6533</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.049</v>
+        <v>-1.0126</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2857</v>
+        <v>0.3592</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0406</v>
+        <v>1.0406</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3849</v>
+        <v>1.202</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0124</v>
+        <v>0.4968</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3725</v>
+        <v>0.7053</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.905</v>
+        <v>-0.5145</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6773</v>
+        <v>-0.463</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2277</v>
+        <v>-0.0515</v>
       </c>
       <c r="G11" t="n">
         <v>1.4156</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9232</v>
+        <v>-0.5327</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2707</v>
+        <v>-0.0946</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0632</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.129</v>
+        <v>-0.9438</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0658</v>
+        <v>0.1738</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9341</v>
+        <v>0.2559</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7358</v>
+        <v>-0.0298</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1984</v>
+        <v>0.2857</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2808</v>
+        <v>0.0192</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7232</v>
+        <v>0.0192</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5576</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6533</v>
+        <v>0.2367</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0126</v>
+        <v>-0.049</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3592</v>
+        <v>0.2857</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1696</v>
+        <v>0.2447</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.64</v>
+        <v>0.0776</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4704</v>
+        <v>0.167</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3898</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1061</v>
+        <v>-0.8265</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2837</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2658</v>
@@ -1468,13 +1468,13 @@
         <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5402</v>
+        <v>-0.0551</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2486</v>
+        <v>0.031</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.3371</v>
+        <v>19.6634</v>
       </c>
       <c r="E14" t="n">
-        <v>9.520899999999999</v>
+        <v>9.847200000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>9.8161</v>
+        <v>9.816299999999996</v>
       </c>
       <c r="G14" t="n">
         <v>11.084</v>
@@ -1534,7 +1534,7 @@
         <v>-10.1048</v>
       </c>
       <c r="O14" t="n">
-        <v>9.491099999999999</v>
+        <v>9.491100000000001</v>
       </c>
       <c r="P14" t="n">
         <v>2.0812</v>
@@ -1546,16 +1546,16 @@
         <v>12.487</v>
       </c>
       <c r="S14" t="n">
-        <v>6.6317</v>
+        <v>6.9579</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8866</v>
+        <v>3.2128</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7451</v>
+        <v>3.7453</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4599</v>
+        <v>-0.4598999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>5.3423</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.259</v>
+        <v>5.8932</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8505</v>
+        <v>7.2791</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5914</v>
+        <v>-1.3859</v>
       </c>
       <c r="G15" t="n">
         <v>3.3799</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.997</v>
+        <v>-1.3629</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5006</v>
+        <v>-1.072</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4964</v>
+        <v>-0.2909</v>
       </c>
       <c r="V15" t="n">
         <v>2.2112</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7655</v>
+        <v>2.264</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8485</v>
+        <v>0.527</v>
       </c>
       <c r="F16" t="n">
-        <v>1.917</v>
+        <v>1.7369</v>
       </c>
       <c r="G16" t="n">
         <v>0.3718</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3719</v>
+        <v>-0.1297</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.109</v>
+        <v>-0.4305</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4809</v>
+        <v>0.3008</v>
       </c>
       <c r="V16" t="n">
         <v>1.3975</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5409</v>
+        <v>0.7464</v>
       </c>
       <c r="E17" t="n">
         <v>0.0653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4756</v>
+        <v>0.6811</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1051</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9564</v>
+        <v>-0.7509</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3171</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6393</v>
+        <v>-0.4338</v>
       </c>
       <c r="V17" t="n">
         <v>0.9376</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.339</v>
+        <v>0.2303</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2909</v>
+        <v>-1.0766</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6299</v>
+        <v>1.3069</v>
       </c>
       <c r="G18" t="n">
         <v>0.7033</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9668</v>
+        <v>-1.0755</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9539</v>
+        <v>-0.7396</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.013</v>
+        <v>-0.3359</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0871</v>
+        <v>-3.4007</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4234</v>
+        <v>-1.1735</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6636</v>
+        <v>-2.2272</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3041</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1586</v>
+        <v>-0.4722</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8663</v>
+        <v>0.1162</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0249</v>
+        <v>-0.5884</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2012</v>
+        <v>-3.7424</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8978</v>
+        <v>-1.1121</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3034</v>
+        <v>-2.6302</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0501</v>
@@ -2014,13 +2014,13 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8084</v>
+        <v>0.2672</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1396</v>
+        <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6688</v>
+        <v>0.3419</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0046</v>
+        <v>-3.7507</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3361</v>
+        <v>-3.229</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6685</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.099</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.657</v>
+        <v>-0.403</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0405</v>
+        <v>0.0667</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6165</v>
+        <v>-0.4697</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5838</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4233</v>
+        <v>-3.9193</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7799</v>
+        <v>-3.5656</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6434</v>
+        <v>-0.3537</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5204</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6323</v>
+        <v>-1.1283</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6929</v>
+        <v>-0.4786</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9394</v>
+        <v>-0.6498</v>
       </c>
       <c r="V22" t="n">
         <v>-0.23</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5741</v>
+        <v>-4.4019</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0891</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4851</v>
+        <v>-3.3128</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7338</v>
@@ -2248,13 +2248,13 @@
         <v>0.2081</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1109</v>
+        <v>0.0613</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2362</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1253</v>
+        <v>0.2975</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9376</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.9512</v>
+        <v>-8.541700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7633</v>
+        <v>-6.4418</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1879</v>
+        <v>-2.0999</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7266</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3329</v>
+        <v>-0.9233</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.901</v>
+        <v>-0.5795</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4318</v>
+        <v>-0.3438</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9376</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.3371</v>
+        <v>-18.62280000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.816200000000002</v>
+        <v>-9.8163</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.520800000000001</v>
+        <v>-8.8065</v>
       </c>
       <c r="G25" t="n">
         <v>-11.0841</v>
@@ -2404,13 +2404,13 @@
         <v>10.4057</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.631600000000001</v>
+        <v>-5.9173</v>
       </c>
       <c r="T25" t="n">
         <v>-3.7453</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.886299999999999</v>
+        <v>-2.1721</v>
       </c>
       <c r="V25" t="n">
         <v>0.4598</v>
